--- a/src/Formatos/Extracto.xlsx
+++ b/src/Formatos/Extracto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanp\Desktop\auto_javarturs\src\Formatos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan Beltran\Desktop\auto_javarturs\src\Formatos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEF7CDA8-8165-4CE8-9420-92C53837A1D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE3E2A1-7030-40DD-A1B8-53D234304AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5505" yWindow="2835" windowWidth="19410" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PLANTILLA" sheetId="78" r:id="rId1"/>
@@ -281,7 +281,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -614,11 +614,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -650,9 +670,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -671,9 +688,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -761,9 +775,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -869,34 +880,58 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1455,124 +1490,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="28"/>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="36"/>
+      <c r="A1" s="26"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="34"/>
     </row>
     <row r="2" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="30"/>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="38"/>
+      <c r="A2" s="28"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="36"/>
     </row>
     <row r="3" spans="1:7" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="32"/>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="40"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="38"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="23"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="22"/>
+      <c r="A4" s="21"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="20"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="23"/>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="22"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="20"/>
     </row>
     <row r="6" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
     </row>
     <row r="7" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="45"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="46"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="44"/>
     </row>
     <row r="8" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="47" t="s">
+      <c r="A8" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="49"/>
+      <c r="B8" s="97"/>
+      <c r="C8" s="97"/>
+      <c r="D8" s="97"/>
+      <c r="E8" s="97"/>
+      <c r="F8" s="97"/>
+      <c r="G8" s="46"/>
     </row>
     <row r="9" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="50" t="s">
+      <c r="A9" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="51"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="52"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="49"/>
     </row>
     <row r="10" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="43"/>
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="41"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
+      <c r="A11" s="13"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="53" t="s">
+      <c r="C11" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53" t="s">
+      <c r="D11" s="50"/>
+      <c r="E11" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="53"/>
-      <c r="G11" s="54"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="51"/>
     </row>
     <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="55" t="s">
+      <c r="A12" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="56"/>
-      <c r="C12" s="21" t="s">
+      <c r="B12" s="53"/>
+      <c r="C12" s="19" t="s">
         <v>43</v>
       </c>
       <c r="D12" s="3"/>
@@ -1581,75 +1616,75 @@
       <c r="G12" s="4"/>
     </row>
     <row r="13" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="55" t="s">
+      <c r="A13" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="56"/>
-      <c r="C13" s="57" t="s">
+      <c r="B13" s="53"/>
+      <c r="C13" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="57"/>
-      <c r="E13" s="17" t="s">
+      <c r="D13" s="54"/>
+      <c r="E13" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="F13" s="17"/>
+      <c r="F13" s="16"/>
       <c r="G13" s="4"/>
     </row>
     <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="55" t="s">
+      <c r="A14" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="56"/>
-      <c r="C14" s="58" t="s">
+      <c r="B14" s="53"/>
+      <c r="C14" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="59"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="56"/>
     </row>
     <row r="15" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="55" t="s">
+      <c r="A15" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="56"/>
-      <c r="C15" s="60" t="s">
+      <c r="B15" s="53"/>
+      <c r="C15" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="61"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="62"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="59"/>
     </row>
     <row r="16" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="63" t="s">
+      <c r="A16" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="64"/>
-      <c r="D16" s="64"/>
-      <c r="E16" s="56" t="s">
+      <c r="B16" s="61"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="56"/>
-      <c r="G16" s="65"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="62"/>
     </row>
     <row r="17" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="66" t="s">
+      <c r="A17" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="67"/>
-      <c r="C17" s="67"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="67"/>
-      <c r="F17" s="67"/>
-      <c r="G17" s="68"/>
+      <c r="B17" s="64"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="64"/>
+      <c r="G17" s="65"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="41" t="s">
+      <c r="A18" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="42"/>
+      <c r="B18" s="40"/>
       <c r="C18" s="5"/>
       <c r="D18" s="6" t="s">
         <v>3</v>
@@ -1657,217 +1692,217 @@
       <c r="E18" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F18" s="69" t="s">
+      <c r="F18" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="70"/>
+      <c r="G18" s="67"/>
     </row>
     <row r="19" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15"/>
+      <c r="A19" s="14"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
-      <c r="D19" s="16">
+      <c r="D19" s="15">
         <v>0</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F19" s="92">
+      <c r="F19" s="87">
         <v>0</v>
       </c>
-      <c r="G19" s="93"/>
+      <c r="G19" s="88"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="41" t="s">
+      <c r="A20" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="40"/>
       <c r="D20" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F20" s="69" t="s">
+      <c r="F20" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="G20" s="70"/>
+      <c r="G20" s="67"/>
     </row>
     <row r="21" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="15"/>
+      <c r="A21" s="14"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
-      <c r="D21" s="16">
+      <c r="D21" s="15">
         <v>0</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="E21" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F21" s="92">
+      <c r="F21" s="87">
         <v>0</v>
       </c>
-      <c r="G21" s="93"/>
+      <c r="G21" s="88"/>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="66" t="s">
+      <c r="A22" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="67"/>
-      <c r="C22" s="67"/>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="68"/>
+      <c r="B22" s="64"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="64"/>
+      <c r="F22" s="64"/>
+      <c r="G22" s="65"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="66" t="s">
+      <c r="A23" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="75"/>
-      <c r="C23" s="76" t="s">
+      <c r="B23" s="72"/>
+      <c r="C23" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="75"/>
+      <c r="D23" s="72"/>
       <c r="E23" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F23" s="76" t="s">
+      <c r="F23" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="G23" s="68"/>
+      <c r="G23" s="65"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="77"/>
-      <c r="B24" s="78"/>
-      <c r="C24" s="79">
+      <c r="A24" s="74"/>
+      <c r="B24" s="75"/>
+      <c r="C24" s="76">
         <v>2006</v>
       </c>
-      <c r="D24" s="78"/>
+      <c r="D24" s="75"/>
       <c r="E24" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F24" s="79" t="s">
+      <c r="F24" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="G24" s="81"/>
+      <c r="G24" s="78"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="66" t="s">
+      <c r="A25" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="67"/>
-      <c r="C25" s="75"/>
-      <c r="D25" s="76" t="s">
+      <c r="B25" s="64"/>
+      <c r="C25" s="72"/>
+      <c r="D25" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="67"/>
-      <c r="F25" s="67"/>
-      <c r="G25" s="68"/>
+      <c r="E25" s="64"/>
+      <c r="F25" s="64"/>
+      <c r="G25" s="65"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="77">
+      <c r="A26" s="74">
         <v>2019</v>
       </c>
-      <c r="B26" s="80"/>
-      <c r="C26" s="78"/>
-      <c r="D26" s="79">
+      <c r="B26" s="77"/>
+      <c r="C26" s="75"/>
+      <c r="D26" s="76">
         <v>336392</v>
       </c>
-      <c r="E26" s="80"/>
-      <c r="F26" s="80"/>
-      <c r="G26" s="81"/>
+      <c r="E26" s="77"/>
+      <c r="F26" s="77"/>
+      <c r="G26" s="78"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="71" t="s">
+      <c r="A27" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="72"/>
+      <c r="B27" s="69"/>
       <c r="C27" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E27" s="24" t="s">
+      <c r="E27" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="F27" s="69" t="s">
+      <c r="F27" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="G27" s="70"/>
+      <c r="G27" s="67"/>
     </row>
     <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="73"/>
-      <c r="B28" s="74"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="82"/>
-      <c r="G28" s="83"/>
+      <c r="A28" s="70"/>
+      <c r="B28" s="71"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="79"/>
+      <c r="G28" s="80"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="71" t="s">
+      <c r="A29" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="72"/>
-      <c r="C29" s="18" t="s">
+      <c r="B29" s="95"/>
+      <c r="C29" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E29" s="24" t="s">
+      <c r="E29" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="F29" s="69" t="s">
+      <c r="F29" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="G29" s="70"/>
+      <c r="G29" s="67"/>
     </row>
     <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="73"/>
-      <c r="B30" s="74"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="84"/>
-      <c r="G30" s="85"/>
+      <c r="A30" s="70"/>
+      <c r="B30" s="89"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="96"/>
+      <c r="G30" s="98"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="71" t="s">
+      <c r="A31" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="72"/>
-      <c r="C31" s="10" t="s">
+      <c r="B31" s="69"/>
+      <c r="C31" s="90" t="s">
         <v>12</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="91" t="s">
         <v>35</v>
       </c>
-      <c r="E31" s="24" t="s">
+      <c r="E31" s="92" t="s">
         <v>36</v>
       </c>
-      <c r="F31" s="69" t="s">
+      <c r="F31" s="93" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="70"/>
+      <c r="G31" s="94"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="73"/>
-      <c r="B32" s="74"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="82"/>
-      <c r="G32" s="83"/>
+      <c r="A32" s="70"/>
+      <c r="B32" s="71"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="79"/>
+      <c r="G32" s="80"/>
     </row>
     <row r="33" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="71" t="s">
+      <c r="A33" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="B33" s="72"/>
-      <c r="C33" s="12" t="s">
+      <c r="B33" s="69"/>
+      <c r="C33" s="11" t="s">
         <v>12</v>
       </c>
       <c r="D33" s="6" t="s">
@@ -1876,92 +1911,92 @@
       <c r="E33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F33" s="69" t="s">
+      <c r="F33" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="G33" s="70"/>
+      <c r="G33" s="67"/>
     </row>
     <row r="34" spans="1:7" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="88"/>
-      <c r="B34" s="89"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="90"/>
-      <c r="G34" s="91"/>
+      <c r="A34" s="83"/>
+      <c r="B34" s="84"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="85"/>
+      <c r="G34" s="86"/>
     </row>
     <row r="35" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="86" t="s">
+      <c r="A37" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="86"/>
-      <c r="C37" s="86"/>
-      <c r="D37" s="86"/>
-      <c r="E37" s="86"/>
-      <c r="F37" s="86"/>
-      <c r="G37" s="86"/>
+      <c r="B37" s="81"/>
+      <c r="C37" s="81"/>
+      <c r="D37" s="81"/>
+      <c r="E37" s="81"/>
+      <c r="F37" s="81"/>
+      <c r="G37" s="81"/>
     </row>
     <row r="38" spans="1:7" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="87" t="s">
+      <c r="A38" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="B38" s="87"/>
-      <c r="C38" s="87"/>
-      <c r="D38" s="87"/>
-      <c r="E38" s="87"/>
-      <c r="F38" s="87"/>
-      <c r="G38" s="87"/>
+      <c r="B38" s="82"/>
+      <c r="C38" s="82"/>
+      <c r="D38" s="82"/>
+      <c r="E38" s="82"/>
+      <c r="F38" s="82"/>
+      <c r="G38" s="82"/>
     </row>
     <row r="39" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="87" t="s">
+      <c r="A39" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="B39" s="87"/>
-      <c r="C39" s="87"/>
-      <c r="D39" s="87"/>
-      <c r="E39" s="87"/>
-      <c r="F39" s="87"/>
-      <c r="G39" s="87"/>
+      <c r="B39" s="82"/>
+      <c r="C39" s="82"/>
+      <c r="D39" s="82"/>
+      <c r="E39" s="82"/>
+      <c r="F39" s="82"/>
+      <c r="G39" s="82"/>
     </row>
     <row r="40" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="87" t="s">
+      <c r="A40" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="B40" s="87"/>
-      <c r="C40" s="87"/>
-      <c r="D40" s="87"/>
-      <c r="E40" s="87"/>
-      <c r="F40" s="87"/>
-      <c r="G40" s="87"/>
+      <c r="B40" s="82"/>
+      <c r="C40" s="82"/>
+      <c r="D40" s="82"/>
+      <c r="E40" s="82"/>
+      <c r="F40" s="82"/>
+      <c r="G40" s="82"/>
     </row>
     <row r="42" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="13"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
+      <c r="A42" s="12"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
     </row>
     <row r="43" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="13"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
+      <c r="A43" s="12"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
     </row>
     <row r="44" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="13"/>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
+      <c r="A44" s="12"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="55">
